--- a/Data/Excel/pcr-data-mix.xlsx
+++ b/Data/Excel/pcr-data-mix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cornellprod-my.sharepoint.com/personal/cjm423_cornell_edu/Documents/study-1-march25/MIX/Data/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1026" documentId="8_{B7E12F50-AE19-4325-ACC3-C71BB40EE95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6C5628B-B529-4CB5-8FA3-009C2EE99236}"/>
+  <xr:revisionPtr revIDLastSave="1030" documentId="8_{B7E12F50-AE19-4325-ACC3-C71BB40EE95D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0473A37C-845B-43D8-9BC5-DC31D379F041}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{248DE185-2CE8-4BA6-8D69-F37F45D83A7F}"/>
+    <workbookView xWindow="28680" yWindow="225" windowWidth="29040" windowHeight="15720" xr2:uid="{248DE185-2CE8-4BA6-8D69-F37F45D83A7F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -86,12 +86,6 @@
     <t>Liver</t>
   </si>
   <si>
-    <t>PRAAK1</t>
-  </si>
-  <si>
-    <t>PRAAK2</t>
-  </si>
-  <si>
     <t>Rep1</t>
   </si>
   <si>
@@ -102,6 +96,12 @@
   </si>
   <si>
     <t>DGAT2</t>
+  </si>
+  <si>
+    <t>PRKAA1</t>
+  </si>
+  <si>
+    <t>PRKAA2</t>
   </si>
 </sst>
 </file>
@@ -480,21 +480,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9608A0BB-4834-4C56-8996-87339C4A28ED}">
   <dimension ref="A1:F508"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.54296875" customWidth="1"/>
-    <col min="10" max="10" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.90625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.453125" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -508,13 +508,13 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -534,7 +534,7 @@
         <v>19.510000000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -554,7 +554,7 @@
         <v>19.02</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -574,7 +574,7 @@
         <v>20.94</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -594,7 +594,7 @@
         <v>20.58</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -614,7 +614,7 @@
         <v>19.96</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -634,7 +634,7 @@
         <v>19.87</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -654,7 +654,7 @@
         <v>20.27</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -674,7 +674,7 @@
         <v>21.02</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -694,7 +694,7 @@
         <v>19.52</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -714,7 +714,7 @@
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -734,7 +734,7 @@
         <v>19.78</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -754,7 +754,7 @@
         <v>20.27</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -774,7 +774,7 @@
         <v>21.05</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -794,7 +794,7 @@
         <v>19.440000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -814,7 +814,7 @@
         <v>21.29</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -834,7 +834,7 @@
         <v>21.54</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -854,7 +854,7 @@
         <v>20.46</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -874,7 +874,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -894,7 +894,7 @@
         <v>19.309999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -914,7 +914,7 @@
         <v>20.309999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -934,7 +934,7 @@
         <v>20.61</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -954,7 +954,7 @@
         <v>19.75</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -974,7 +974,7 @@
         <v>19.3</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -994,7 +994,7 @@
         <v>20.55</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>20.329999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>20.149999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -1054,7 +1054,7 @@
         <v>20.13</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>19.600000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -1094,7 +1094,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -1114,7 +1114,7 @@
         <v>21.65</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -1134,7 +1134,7 @@
         <v>20.79</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -1154,7 +1154,7 @@
         <v>21.32</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -1174,7 +1174,7 @@
         <v>19.84</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>20.89</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>21.85</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>21.79</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>21.31</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>21.11</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -1294,7 +1294,7 @@
         <v>20.05</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>4</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>24.02</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -1334,7 +1334,7 @@
         <v>23.64</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>23.74</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>23.95</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>23.12</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>24.07</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>23.58</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>4</v>
       </c>
@@ -1454,7 +1454,7 @@
         <v>24.16</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>4</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>24.46</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -1494,7 +1494,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>4</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>24.94</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>4</v>
       </c>
@@ -1534,7 +1534,7 @@
         <v>23.55</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>24.04</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>4</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>22.92</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>4</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>24.41</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>4</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>24.39</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>4</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>23.68</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>4</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>24.67</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>4</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>25.55</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>4</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>24.03</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>4</v>
       </c>
@@ -1714,7 +1714,7 @@
         <v>24.76</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>4</v>
       </c>
@@ -1734,7 +1734,7 @@
         <v>23.24</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>4</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>23.74</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>4</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>25.8</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>4</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>25.42</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>4</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>24.14</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>4</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>25.57</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>4</v>
       </c>
@@ -1854,7 +1854,7 @@
         <v>24.97</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>4</v>
       </c>
@@ -1874,7 +1874,7 @@
         <v>23.23</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>4</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>25.31</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>4</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>24.74</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>4</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>23.94</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>4</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>23.66</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>4</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>22.85</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>4</v>
       </c>
@@ -1994,7 +1994,7 @@
         <v>23.79</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>4</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>23.94</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>4</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>23.78</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>4</v>
       </c>
@@ -2054,7 +2054,7 @@
         <v>23.58</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>4</v>
       </c>
@@ -2074,7 +2074,7 @@
         <v>23.85</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>4</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>21.11</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>4</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>21.35</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>4</v>
       </c>
@@ -2134,7 +2134,7 @@
         <v>21.45</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>4</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>20.72</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>4</v>
       </c>
@@ -2174,7 +2174,7 @@
         <v>20.53</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>4</v>
       </c>
@@ -2194,7 +2194,7 @@
         <v>20.86</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>4</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>21.32</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>4</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>21.55</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>4</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>20.87</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>4</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>21.26</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>4</v>
       </c>
@@ -2294,7 +2294,7 @@
         <v>21.81</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>4</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>21.19</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>4</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>21.13</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>4</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>20.13</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>4</v>
       </c>
@@ -2374,7 +2374,7 @@
         <v>21.66</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>4</v>
       </c>
@@ -2394,7 +2394,7 @@
         <v>22.11</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>4</v>
       </c>
@@ -2414,7 +2414,7 @@
         <v>21.72</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>4</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>22.45</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>4</v>
       </c>
@@ -2454,7 +2454,7 @@
         <v>21.44</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>4</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>22.18</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>4</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>21.95</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>4</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>21.38</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>4</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>20.93</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>4</v>
       </c>
@@ -2554,7 +2554,7 @@
         <v>22.27</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>4</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>23.73</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>4</v>
       </c>
@@ -2594,7 +2594,7 @@
         <v>22.41</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>4</v>
       </c>
@@ -2614,7 +2614,7 @@
         <v>23.19</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>4</v>
       </c>
@@ -2634,7 +2634,7 @@
         <v>23.25</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>4</v>
       </c>
@@ -2654,7 +2654,7 @@
         <v>23.33</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>4</v>
       </c>
@@ -2674,7 +2674,7 @@
         <v>24.18</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>4</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>23.08</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>4</v>
       </c>
@@ -2714,7 +2714,7 @@
         <v>22.62</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>4</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>22.96</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>4</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>22.78</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>4</v>
       </c>
@@ -2774,7 +2774,7 @@
         <v>22.78</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>4</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>22.38</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>4</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>22.44</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>4</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>22.11</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>4</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>22.79</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>4</v>
       </c>
@@ -2874,7 +2874,7 @@
         <v>24.28</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>4</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>24.16</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>4</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>23.63</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>4</v>
       </c>
@@ -2934,7 +2934,7 @@
         <v>24.34</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>4</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>24.43</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>4</v>
       </c>
@@ -2974,7 +2974,7 @@
         <v>23.78</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>4</v>
       </c>
@@ -2994,7 +2994,7 @@
         <v>24.22</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>4</v>
       </c>
@@ -3014,7 +3014,7 @@
         <v>24.32</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>4</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>24.08</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>4</v>
       </c>
@@ -3054,7 +3054,7 @@
         <v>25.38</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>4</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>25.49</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>4</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>24.89</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>4</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>24.84</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>4</v>
       </c>
@@ -3134,7 +3134,7 @@
         <v>23.59</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>4</v>
       </c>
@@ -3154,7 +3154,7 @@
         <v>24.8</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>4</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>24.02</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>4</v>
       </c>
@@ -3194,7 +3194,7 @@
         <v>23.68</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>4</v>
       </c>
@@ -3214,7 +3214,7 @@
         <v>25.75</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>4</v>
       </c>
@@ -3234,7 +3234,7 @@
         <v>27.18</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>4</v>
       </c>
@@ -3254,7 +3254,7 @@
         <v>25.69</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>4</v>
       </c>
@@ -3274,7 +3274,7 @@
         <v>26.06</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>4</v>
       </c>
@@ -3294,7 +3294,7 @@
         <v>23.87</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>4</v>
       </c>
@@ -3314,7 +3314,7 @@
         <v>24.15</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>4</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>27.37</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>4</v>
       </c>
@@ -3354,7 +3354,7 @@
         <v>26.45</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>4</v>
       </c>
@@ -3374,7 +3374,7 @@
         <v>23.77</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>4</v>
       </c>
@@ -3394,7 +3394,7 @@
         <v>26.85</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>4</v>
       </c>
@@ -3414,7 +3414,7 @@
         <v>26.28</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>4</v>
       </c>
@@ -3434,7 +3434,7 @@
         <v>25.93</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>4</v>
       </c>
@@ -3454,7 +3454,7 @@
         <v>28.31</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>4</v>
       </c>
@@ -3474,7 +3474,7 @@
         <v>25.64</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>4</v>
       </c>
@@ -3494,7 +3494,7 @@
         <v>25.71</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>4</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>25.33</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>4</v>
       </c>
@@ -3534,7 +3534,7 @@
         <v>24.12</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>4</v>
       </c>
@@ -3554,7 +3554,7 @@
         <v>24.56</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>4</v>
       </c>
@@ -3574,7 +3574,7 @@
         <v>25.67</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>4</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>24.42</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>4</v>
       </c>
@@ -3614,7 +3614,7 @@
         <v>25.09</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>4</v>
       </c>
@@ -3634,7 +3634,7 @@
         <v>24.43</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>14</v>
       </c>
@@ -3654,7 +3654,7 @@
         <v>20.32</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>14</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>20.7</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>14</v>
       </c>
@@ -3694,7 +3694,7 @@
         <v>20.38</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>14</v>
       </c>
@@ -3714,7 +3714,7 @@
         <v>20.53</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>14</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>21.58</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>14</v>
       </c>
@@ -3754,7 +3754,7 @@
         <v>20.53</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>14</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>20.85</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>14</v>
       </c>
@@ -3794,7 +3794,7 @@
         <v>21.51</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>14</v>
       </c>
@@ -3814,7 +3814,7 @@
         <v>21.99</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>14</v>
       </c>
@@ -3834,7 +3834,7 @@
         <v>20.07</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>14</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>20.38</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>14</v>
       </c>
@@ -3874,7 +3874,7 @@
         <v>21.12</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>14</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>21.98</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>14</v>
       </c>
@@ -3914,7 +3914,7 @@
         <v>22.01</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>14</v>
       </c>
@@ -3934,7 +3934,7 @@
         <v>21.11</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>14</v>
       </c>
@@ -3954,7 +3954,7 @@
         <v>20.239999999999998</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>14</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>19.29</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>14</v>
       </c>
@@ -3994,7 +3994,7 @@
         <v>19.82</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>14</v>
       </c>
@@ -4014,7 +4014,7 @@
         <v>19.059999999999999</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>14</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>21.33</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>14</v>
       </c>
@@ -4054,7 +4054,7 @@
         <v>20.87</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>14</v>
       </c>
@@ -4074,7 +4074,7 @@
         <v>20.010000000000002</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>14</v>
       </c>
@@ -4094,7 +4094,7 @@
         <v>19.559999999999999</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>14</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>20.25</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>14</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>20.350000000000001</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>14</v>
       </c>
@@ -4154,7 +4154,7 @@
         <v>19.260000000000002</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>14</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>21.34</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>14</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>20.190000000000001</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>14</v>
       </c>
@@ -4214,7 +4214,7 @@
         <v>20.57</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>14</v>
       </c>
@@ -4234,7 +4234,7 @@
         <v>20.88</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>14</v>
       </c>
@@ -4254,7 +4254,7 @@
         <v>20.73</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>14</v>
       </c>
@@ -4274,7 +4274,7 @@
         <v>21.29</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>14</v>
       </c>
@@ -4294,7 +4294,7 @@
         <v>20.39</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>14</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>20.96</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>14</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>20.329999999999998</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>14</v>
       </c>
@@ -4354,7 +4354,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>14</v>
       </c>
@@ -4374,7 +4374,7 @@
         <v>20.170000000000002</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>14</v>
       </c>
@@ -4394,7 +4394,7 @@
         <v>20.22</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>14</v>
       </c>
@@ -4414,7 +4414,7 @@
         <v>21.03</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>14</v>
       </c>
@@ -4434,7 +4434,7 @@
         <v>22.27</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>14</v>
       </c>
@@ -4454,7 +4454,7 @@
         <v>21.8</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>14</v>
       </c>
@@ -4474,7 +4474,7 @@
         <v>21.96</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>14</v>
       </c>
@@ -4494,7 +4494,7 @@
         <v>21.28</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>14</v>
       </c>
@@ -4514,7 +4514,7 @@
         <v>22.53</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>14</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>23.36</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>14</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>14</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>21.25</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>14</v>
       </c>
@@ -4594,7 +4594,7 @@
         <v>22.11</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>14</v>
       </c>
@@ -4614,7 +4614,7 @@
         <v>23.57</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>14</v>
       </c>
@@ -4634,7 +4634,7 @@
         <v>23.2</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>14</v>
       </c>
@@ -4654,7 +4654,7 @@
         <v>23.12</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>14</v>
       </c>
@@ -4674,7 +4674,7 @@
         <v>23.57</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>14</v>
       </c>
@@ -4694,7 +4694,7 @@
         <v>22.92</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>14</v>
       </c>
@@ -4714,7 +4714,7 @@
         <v>23.08</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>14</v>
       </c>
@@ -4734,7 +4734,7 @@
         <v>21.21</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>14</v>
       </c>
@@ -4754,7 +4754,7 @@
         <v>22.44</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>14</v>
       </c>
@@ -4774,7 +4774,7 @@
         <v>21.22</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>14</v>
       </c>
@@ -4794,7 +4794,7 @@
         <v>21.42</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>14</v>
       </c>
@@ -4814,7 +4814,7 @@
         <v>22.28</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>14</v>
       </c>
@@ -4834,7 +4834,7 @@
         <v>21.46</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>14</v>
       </c>
@@ -4854,7 +4854,7 @@
         <v>20.46</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>14</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>21.23</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>14</v>
       </c>
@@ -4894,7 +4894,7 @@
         <v>22.71</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>14</v>
       </c>
@@ -4914,7 +4914,7 @@
         <v>20.29</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>14</v>
       </c>
@@ -4934,7 +4934,7 @@
         <v>18.21</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>14</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>22.29</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>14</v>
       </c>
@@ -4974,7 +4974,7 @@
         <v>22.4</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>14</v>
       </c>
@@ -4994,7 +4994,7 @@
         <v>20.71</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>14</v>
       </c>
@@ -5014,7 +5014,7 @@
         <v>20.260000000000002</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>14</v>
       </c>
@@ -5034,7 +5034,7 @@
         <v>20.13</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>14</v>
       </c>
@@ -5054,7 +5054,7 @@
         <v>26.27</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>14</v>
       </c>
@@ -5074,7 +5074,7 @@
         <v>22.6</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>14</v>
       </c>
@@ -5094,7 +5094,7 @@
         <v>23.03</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>14</v>
       </c>
@@ -5114,7 +5114,7 @@
         <v>23.65</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>14</v>
       </c>
@@ -5134,7 +5134,7 @@
         <v>22.64</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>14</v>
       </c>
@@ -5154,7 +5154,7 @@
         <v>22.01</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>14</v>
       </c>
@@ -5174,7 +5174,7 @@
         <v>23.61</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>14</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>23.44</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>14</v>
       </c>
@@ -5214,7 +5214,7 @@
         <v>23.16</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>14</v>
       </c>
@@ -5234,7 +5234,7 @@
         <v>22.81</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>14</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>24.02</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>14</v>
       </c>
@@ -5274,7 +5274,7 @@
         <v>22.92</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>14</v>
       </c>
@@ -5294,7 +5294,7 @@
         <v>22.31</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>14</v>
       </c>
@@ -5314,7 +5314,7 @@
         <v>22.28</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>14</v>
       </c>
@@ -5334,7 +5334,7 @@
         <v>22.12</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>14</v>
       </c>
@@ -5354,7 +5354,7 @@
         <v>23.47</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>14</v>
       </c>
@@ -5374,7 +5374,7 @@
         <v>24.58</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>14</v>
       </c>
@@ -5394,7 +5394,7 @@
         <v>24.18</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>14</v>
       </c>
@@ -5414,7 +5414,7 @@
         <v>25.54</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>14</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v>24.51</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>14</v>
       </c>
@@ -5454,7 +5454,7 @@
         <v>25.64</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>14</v>
       </c>
@@ -5474,7 +5474,7 @@
         <v>24.98</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>14</v>
       </c>
@@ -5494,7 +5494,7 @@
         <v>24.44</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>14</v>
       </c>
@@ -5514,7 +5514,7 @@
         <v>23.67</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>14</v>
       </c>
@@ -5534,7 +5534,7 @@
         <v>23.18</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>14</v>
       </c>
@@ -5554,7 +5554,7 @@
         <v>24.14</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>14</v>
       </c>
@@ -5574,7 +5574,7 @@
         <v>23.01</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>14</v>
       </c>
@@ -5594,7 +5594,7 @@
         <v>24.55</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>14</v>
       </c>
@@ -5614,7 +5614,7 @@
         <v>23.68</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>14</v>
       </c>
@@ -5634,7 +5634,7 @@
         <v>23.28</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>14</v>
       </c>
@@ -5654,7 +5654,7 @@
         <v>24.14</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>14</v>
       </c>
@@ -5674,7 +5674,7 @@
         <v>24.02</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>14</v>
       </c>
@@ -5694,7 +5694,7 @@
         <v>23.02</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>14</v>
       </c>
@@ -5714,7 +5714,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>14</v>
       </c>
@@ -5734,7 +5734,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>14</v>
       </c>
@@ -5754,7 +5754,7 @@
         <v>25.22</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>14</v>
       </c>
@@ -5774,7 +5774,7 @@
         <v>22.76</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>14</v>
       </c>
@@ -5794,7 +5794,7 @@
         <v>22.86</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>14</v>
       </c>
@@ -5814,7 +5814,7 @@
         <v>22.75</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>14</v>
       </c>
@@ -5834,7 +5834,7 @@
         <v>23.97</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>14</v>
       </c>
@@ -5854,7 +5854,7 @@
         <v>26.13</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>14</v>
       </c>
@@ -5874,7 +5874,7 @@
         <v>26.02</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>14</v>
       </c>
@@ -5894,7 +5894,7 @@
         <v>23.38</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>14</v>
       </c>
@@ -5914,7 +5914,7 @@
         <v>24.08</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>14</v>
       </c>
@@ -5934,7 +5934,7 @@
         <v>22.92</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>14</v>
       </c>
@@ -5954,7 +5954,7 @@
         <v>23.73</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>14</v>
       </c>
@@ -5974,7 +5974,7 @@
         <v>26.89</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>14</v>
       </c>
@@ -5994,7 +5994,7 @@
         <v>24.94</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>14</v>
       </c>
@@ -6014,7 +6014,7 @@
         <v>25.01</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>14</v>
       </c>
@@ -6034,7 +6034,7 @@
         <v>25.03</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>14</v>
       </c>
@@ -6054,7 +6054,7 @@
         <v>24.71</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>14</v>
       </c>
@@ -6074,7 +6074,7 @@
         <v>24.63</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>14</v>
       </c>
@@ -6094,7 +6094,7 @@
         <v>23.36</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>14</v>
       </c>
@@ -6114,7 +6114,7 @@
         <v>25.19</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>14</v>
       </c>
@@ -6134,7 +6134,7 @@
         <v>26.01</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>14</v>
       </c>
@@ -6154,7 +6154,7 @@
         <v>25.52</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>14</v>
       </c>
@@ -6174,7 +6174,7 @@
         <v>25.01</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>14</v>
       </c>
@@ -6194,7 +6194,7 @@
         <v>25.51</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>14</v>
       </c>
@@ -6214,7 +6214,7 @@
         <v>24.96</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>14</v>
       </c>
@@ -6234,7 +6234,7 @@
         <v>26.79</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>14</v>
       </c>
@@ -6254,7 +6254,7 @@
         <v>24.79</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>14</v>
       </c>
@@ -6274,7 +6274,7 @@
         <v>24.79</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>14</v>
       </c>
@@ -6294,7 +6294,7 @@
         <v>26.21</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>14</v>
       </c>
@@ -6314,7 +6314,7 @@
         <v>26.15</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>14</v>
       </c>
@@ -6334,7 +6334,7 @@
         <v>25.49</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>14</v>
       </c>
@@ -6354,7 +6354,7 @@
         <v>25.01</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>14</v>
       </c>
@@ -6374,7 +6374,7 @@
         <v>24.63</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>14</v>
       </c>
@@ -6394,7 +6394,7 @@
         <v>25.83</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>14</v>
       </c>
@@ -6414,7 +6414,7 @@
         <v>24.51</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>14</v>
       </c>
@@ -6434,7 +6434,7 @@
         <v>25.4</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>14</v>
       </c>
@@ -6454,7 +6454,7 @@
         <v>26.56</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>14</v>
       </c>
@@ -6474,7 +6474,7 @@
         <v>26.88</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>14</v>
       </c>
@@ -6494,7 +6494,7 @@
         <v>24.22</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>14</v>
       </c>
@@ -6514,7 +6514,7 @@
         <v>26.17</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>14</v>
       </c>
@@ -6534,7 +6534,7 @@
         <v>27.48</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>14</v>
       </c>
@@ -6554,7 +6554,7 @@
         <v>25.1</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>14</v>
       </c>
@@ -6574,7 +6574,7 @@
         <v>26.06</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>14</v>
       </c>
@@ -6594,7 +6594,7 @@
         <v>25.85</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>14</v>
       </c>
@@ -6614,7 +6614,7 @@
         <v>27.91</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>14</v>
       </c>
@@ -6634,7 +6634,7 @@
         <v>28.24</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>14</v>
       </c>
@@ -6654,7 +6654,7 @@
         <v>26.54</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>14</v>
       </c>
@@ -6674,7 +6674,7 @@
         <v>27.85</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>14</v>
       </c>
@@ -6694,7 +6694,7 @@
         <v>26.35</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>14</v>
       </c>
@@ -6714,7 +6714,7 @@
         <v>27.53</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>14</v>
       </c>
@@ -6734,7 +6734,7 @@
         <v>26.28</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>14</v>
       </c>
@@ -6754,7 +6754,7 @@
         <v>27.11</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>15</v>
       </c>
@@ -6774,7 +6774,7 @@
         <v>20.71</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>15</v>
       </c>
@@ -6794,7 +6794,7 @@
         <v>20.420000000000002</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>15</v>
       </c>
@@ -6814,7 +6814,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>15</v>
       </c>
@@ -6834,7 +6834,7 @@
         <v>19.260000000000002</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>15</v>
       </c>
@@ -6854,7 +6854,7 @@
         <v>19.059999999999999</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>15</v>
       </c>
@@ -6874,7 +6874,7 @@
         <v>19.18</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>15</v>
       </c>
@@ -6894,7 +6894,7 @@
         <v>18.12</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>15</v>
       </c>
@@ -6914,7 +6914,7 @@
         <v>18.39</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>15</v>
       </c>
@@ -6934,7 +6934,7 @@
         <v>19.940000000000001</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>15</v>
       </c>
@@ -6954,7 +6954,7 @@
         <v>20.12</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>15</v>
       </c>
@@ -6974,7 +6974,7 @@
         <v>20.03</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>15</v>
       </c>
@@ -6994,7 +6994,7 @@
         <v>19.760000000000002</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>15</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>19.54</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>15</v>
       </c>
@@ -7034,7 +7034,7 @@
         <v>21.6</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>15</v>
       </c>
@@ -7054,7 +7054,7 @@
         <v>20.45</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>15</v>
       </c>
@@ -7074,7 +7074,7 @@
         <v>20.89</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>15</v>
       </c>
@@ -7094,7 +7094,7 @@
         <v>20.25</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>15</v>
       </c>
@@ -7114,7 +7114,7 @@
         <v>19.55</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>15</v>
       </c>
@@ -7134,7 +7134,7 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>15</v>
       </c>
@@ -7154,7 +7154,7 @@
         <v>20.37</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>15</v>
       </c>
@@ -7174,7 +7174,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>15</v>
       </c>
@@ -7194,7 +7194,7 @@
         <v>20.88</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>15</v>
       </c>
@@ -7214,7 +7214,7 @@
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>15</v>
       </c>
@@ -7234,7 +7234,7 @@
         <v>20.07</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>15</v>
       </c>
@@ -7254,7 +7254,7 @@
         <v>19.52</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>15</v>
       </c>
@@ -7274,7 +7274,7 @@
         <v>20.71</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>15</v>
       </c>
@@ -7294,7 +7294,7 @@
         <v>19.23</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>15</v>
       </c>
@@ -7314,7 +7314,7 @@
         <v>20.190000000000001</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>15</v>
       </c>
@@ -7334,7 +7334,7 @@
         <v>20.260000000000002</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>15</v>
       </c>
@@ -7354,7 +7354,7 @@
         <v>20.43</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>15</v>
       </c>
@@ -7374,7 +7374,7 @@
         <v>20.69</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>15</v>
       </c>
@@ -7394,7 +7394,7 @@
         <v>19.510000000000002</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>15</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>19.239999999999998</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>15</v>
       </c>
@@ -7434,7 +7434,7 @@
         <v>20.190000000000001</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>15</v>
       </c>
@@ -7454,7 +7454,7 @@
         <v>19.66</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>15</v>
       </c>
@@ -7474,7 +7474,7 @@
         <v>21.17</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>15</v>
       </c>
@@ -7494,7 +7494,7 @@
         <v>21.83</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>15</v>
       </c>
@@ -7514,7 +7514,7 @@
         <v>20.440000000000001</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>15</v>
       </c>
@@ -7534,7 +7534,7 @@
         <v>20.46</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>15</v>
       </c>
@@ -7545,7 +7545,7 @@
         <v>1</v>
       </c>
       <c r="D353" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E353">
         <v>27.88</v>
@@ -7554,7 +7554,7 @@
         <v>27.51</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>15</v>
       </c>
@@ -7565,7 +7565,7 @@
         <v>2</v>
       </c>
       <c r="D354" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E354">
         <v>26.78</v>
@@ -7574,7 +7574,7 @@
         <v>25.74</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>15</v>
       </c>
@@ -7585,7 +7585,7 @@
         <v>3</v>
       </c>
       <c r="D355" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E355">
         <v>26.03</v>
@@ -7594,7 +7594,7 @@
         <v>26.05</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>15</v>
       </c>
@@ -7605,7 +7605,7 @@
         <v>4</v>
       </c>
       <c r="D356" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E356">
         <v>25.41</v>
@@ -7614,7 +7614,7 @@
         <v>25.73</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>15</v>
       </c>
@@ -7625,7 +7625,7 @@
         <v>5</v>
       </c>
       <c r="D357" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E357">
         <v>25.61</v>
@@ -7634,7 +7634,7 @@
         <v>26.03</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>15</v>
       </c>
@@ -7645,7 +7645,7 @@
         <v>6</v>
       </c>
       <c r="D358" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E358">
         <v>25.78</v>
@@ -7654,7 +7654,7 @@
         <v>25.15</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>15</v>
       </c>
@@ -7665,7 +7665,7 @@
         <v>7</v>
       </c>
       <c r="D359" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E359">
         <v>25.3</v>
@@ -7674,7 +7674,7 @@
         <v>24.3</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>15</v>
       </c>
@@ -7685,7 +7685,7 @@
         <v>8</v>
       </c>
       <c r="D360" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E360">
         <v>24.99</v>
@@ -7694,7 +7694,7 @@
         <v>25.75</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>15</v>
       </c>
@@ -7705,7 +7705,7 @@
         <v>1</v>
       </c>
       <c r="D361" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E361">
         <v>26.36</v>
@@ -7714,7 +7714,7 @@
         <v>26.89</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>15</v>
       </c>
@@ -7725,7 +7725,7 @@
         <v>2</v>
       </c>
       <c r="D362" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E362">
         <v>26.97</v>
@@ -7734,7 +7734,7 @@
         <v>26.94</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>15</v>
       </c>
@@ -7745,7 +7745,7 @@
         <v>3</v>
       </c>
       <c r="D363" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E363">
         <v>26.39</v>
@@ -7754,7 +7754,7 @@
         <v>26.67</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>15</v>
       </c>
@@ -7765,7 +7765,7 @@
         <v>4</v>
       </c>
       <c r="D364" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E364">
         <v>25.43</v>
@@ -7774,7 +7774,7 @@
         <v>26.1</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>15</v>
       </c>
@@ -7785,7 +7785,7 @@
         <v>5</v>
       </c>
       <c r="D365" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E365">
         <v>24.74</v>
@@ -7794,7 +7794,7 @@
         <v>24.24</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>15</v>
       </c>
@@ -7805,7 +7805,7 @@
         <v>6</v>
       </c>
       <c r="D366" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E366">
         <v>25.67</v>
@@ -7814,7 +7814,7 @@
         <v>25.47</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>15</v>
       </c>
@@ -7825,7 +7825,7 @@
         <v>7</v>
       </c>
       <c r="D367" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E367">
         <v>26.68</v>
@@ -7834,7 +7834,7 @@
         <v>26.18</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>15</v>
       </c>
@@ -7845,7 +7845,7 @@
         <v>1</v>
       </c>
       <c r="D368" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E368">
         <v>26.27</v>
@@ -7854,7 +7854,7 @@
         <v>26.45</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>15</v>
       </c>
@@ -7865,7 +7865,7 @@
         <v>2</v>
       </c>
       <c r="D369" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E369">
         <v>25.42</v>
@@ -7874,7 +7874,7 @@
         <v>25.53</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>15</v>
       </c>
@@ -7885,7 +7885,7 @@
         <v>3</v>
       </c>
       <c r="D370" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E370">
         <v>25.73</v>
@@ -7894,7 +7894,7 @@
         <v>26.08</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>15</v>
       </c>
@@ -7905,7 +7905,7 @@
         <v>4</v>
       </c>
       <c r="D371" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E371">
         <v>26.77</v>
@@ -7914,7 +7914,7 @@
         <v>26.89</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>15</v>
       </c>
@@ -7925,7 +7925,7 @@
         <v>5</v>
       </c>
       <c r="D372" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E372">
         <v>26.27</v>
@@ -7934,7 +7934,7 @@
         <v>27.04</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>15</v>
       </c>
@@ -7945,7 +7945,7 @@
         <v>6</v>
       </c>
       <c r="D373" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E373">
         <v>25.42</v>
@@ -7954,7 +7954,7 @@
         <v>25.78</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>15</v>
       </c>
@@ -7965,7 +7965,7 @@
         <v>7</v>
       </c>
       <c r="D374" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E374">
         <v>26.62</v>
@@ -7974,7 +7974,7 @@
         <v>26.95</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>15</v>
       </c>
@@ -7985,7 +7985,7 @@
         <v>8</v>
       </c>
       <c r="D375" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E375">
         <v>25.97</v>
@@ -7994,7 +7994,7 @@
         <v>25.36</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>15</v>
       </c>
@@ -8005,7 +8005,7 @@
         <v>1</v>
       </c>
       <c r="D376" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E376">
         <v>25.33</v>
@@ -8014,7 +8014,7 @@
         <v>25.68</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>15</v>
       </c>
@@ -8025,7 +8025,7 @@
         <v>2</v>
       </c>
       <c r="D377" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E377">
         <v>26.14</v>
@@ -8034,7 +8034,7 @@
         <v>25.07</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>15</v>
       </c>
@@ -8045,7 +8045,7 @@
         <v>3</v>
       </c>
       <c r="D378" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E378">
         <v>27.1</v>
@@ -8054,7 +8054,7 @@
         <v>26.8</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>15</v>
       </c>
@@ -8065,7 +8065,7 @@
         <v>4</v>
       </c>
       <c r="D379" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E379">
         <v>24.66</v>
@@ -8074,7 +8074,7 @@
         <v>24.27</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>15</v>
       </c>
@@ -8085,7 +8085,7 @@
         <v>5</v>
       </c>
       <c r="D380" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E380">
         <v>26.67</v>
@@ -8094,7 +8094,7 @@
         <v>26.35</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>15</v>
       </c>
@@ -8105,7 +8105,7 @@
         <v>6</v>
       </c>
       <c r="D381" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E381">
         <v>26.17</v>
@@ -8114,7 +8114,7 @@
         <v>26.22</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>15</v>
       </c>
@@ -8125,7 +8125,7 @@
         <v>7</v>
       </c>
       <c r="D382" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E382">
         <v>26.89</v>
@@ -8134,7 +8134,7 @@
         <v>26.49</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>15</v>
       </c>
@@ -8145,7 +8145,7 @@
         <v>8</v>
       </c>
       <c r="D383" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E383">
         <v>25.67</v>
@@ -8154,7 +8154,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>15</v>
       </c>
@@ -8165,7 +8165,7 @@
         <v>1</v>
       </c>
       <c r="D384" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E384">
         <v>25.11</v>
@@ -8174,7 +8174,7 @@
         <v>25.78</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>15</v>
       </c>
@@ -8185,7 +8185,7 @@
         <v>2</v>
       </c>
       <c r="D385" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E385">
         <v>22.3</v>
@@ -8194,7 +8194,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>15</v>
       </c>
@@ -8205,7 +8205,7 @@
         <v>3</v>
       </c>
       <c r="D386" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E386">
         <v>24.02</v>
@@ -8214,7 +8214,7 @@
         <v>23.12</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>15</v>
       </c>
@@ -8225,7 +8225,7 @@
         <v>4</v>
       </c>
       <c r="D387" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E387">
         <v>24.83</v>
@@ -8234,7 +8234,7 @@
         <v>24.83</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>15</v>
       </c>
@@ -8245,7 +8245,7 @@
         <v>5</v>
       </c>
       <c r="D388" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E388">
         <v>25.38</v>
@@ -8254,7 +8254,7 @@
         <v>25.01</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>15</v>
       </c>
@@ -8265,7 +8265,7 @@
         <v>6</v>
       </c>
       <c r="D389" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E389">
         <v>27.68</v>
@@ -8274,7 +8274,7 @@
         <v>27.2</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>15</v>
       </c>
@@ -8285,7 +8285,7 @@
         <v>7</v>
       </c>
       <c r="D390" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E390">
         <v>26.11</v>
@@ -8294,7 +8294,7 @@
         <v>26.62</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>15</v>
       </c>
@@ -8305,7 +8305,7 @@
         <v>8</v>
       </c>
       <c r="D391" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E391">
         <v>23.72</v>
@@ -8314,7 +8314,7 @@
         <v>22.78</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>15</v>
       </c>
@@ -8325,7 +8325,7 @@
         <v>1</v>
       </c>
       <c r="D392" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E392">
         <v>28.72</v>
@@ -8334,7 +8334,7 @@
         <v>29.23</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>15</v>
       </c>
@@ -8345,7 +8345,7 @@
         <v>2</v>
       </c>
       <c r="D393" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E393">
         <v>27.1</v>
@@ -8354,7 +8354,7 @@
         <v>27.32</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>15</v>
       </c>
@@ -8365,7 +8365,7 @@
         <v>3</v>
       </c>
       <c r="D394" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E394">
         <v>26.29</v>
@@ -8374,7 +8374,7 @@
         <v>26.75</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>15</v>
       </c>
@@ -8385,7 +8385,7 @@
         <v>4</v>
       </c>
       <c r="D395" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E395">
         <v>25.61</v>
@@ -8394,7 +8394,7 @@
         <v>25.39</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>15</v>
       </c>
@@ -8405,7 +8405,7 @@
         <v>5</v>
       </c>
       <c r="D396" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E396">
         <v>25.55</v>
@@ -8414,7 +8414,7 @@
         <v>25.82</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>15</v>
       </c>
@@ -8425,7 +8425,7 @@
         <v>6</v>
       </c>
       <c r="D397" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E397">
         <v>25.51</v>
@@ -8434,7 +8434,7 @@
         <v>25.53</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>15</v>
       </c>
@@ -8445,7 +8445,7 @@
         <v>7</v>
       </c>
       <c r="D398" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E398">
         <v>23.95</v>
@@ -8454,7 +8454,7 @@
         <v>24.98</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>15</v>
       </c>
@@ -8465,7 +8465,7 @@
         <v>8</v>
       </c>
       <c r="D399" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E399">
         <v>25.39</v>
@@ -8474,7 +8474,7 @@
         <v>25.47</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>15</v>
       </c>
@@ -8485,7 +8485,7 @@
         <v>1</v>
       </c>
       <c r="D400" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E400">
         <v>27.94</v>
@@ -8494,7 +8494,7 @@
         <v>27.98</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>15</v>
       </c>
@@ -8505,7 +8505,7 @@
         <v>2</v>
       </c>
       <c r="D401" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E401">
         <v>27.65</v>
@@ -8514,7 +8514,7 @@
         <v>27.45</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>15</v>
       </c>
@@ -8525,7 +8525,7 @@
         <v>3</v>
       </c>
       <c r="D402" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E402">
         <v>27.52</v>
@@ -8534,7 +8534,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>15</v>
       </c>
@@ -8545,7 +8545,7 @@
         <v>4</v>
       </c>
       <c r="D403" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E403">
         <v>26.17</v>
@@ -8554,7 +8554,7 @@
         <v>26.23</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>15</v>
       </c>
@@ -8565,7 +8565,7 @@
         <v>5</v>
       </c>
       <c r="D404" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E404">
         <v>26.87</v>
@@ -8574,7 +8574,7 @@
         <v>27.05</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>15</v>
       </c>
@@ -8585,7 +8585,7 @@
         <v>6</v>
       </c>
       <c r="D405" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E405">
         <v>27.6</v>
@@ -8594,7 +8594,7 @@
         <v>27.37</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>15</v>
       </c>
@@ -8605,7 +8605,7 @@
         <v>7</v>
       </c>
       <c r="D406" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E406">
         <v>27.4</v>
@@ -8614,7 +8614,7 @@
         <v>27.12</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>15</v>
       </c>
@@ -8625,7 +8625,7 @@
         <v>1</v>
       </c>
       <c r="D407" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E407">
         <v>26.83</v>
@@ -8634,7 +8634,7 @@
         <v>26.94</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>15</v>
       </c>
@@ -8645,7 +8645,7 @@
         <v>2</v>
       </c>
       <c r="D408" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E408">
         <v>26.22</v>
@@ -8654,7 +8654,7 @@
         <v>26.07</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>15</v>
       </c>
@@ -8665,7 +8665,7 @@
         <v>3</v>
       </c>
       <c r="D409" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E409">
         <v>26.26</v>
@@ -8674,7 +8674,7 @@
         <v>26.69</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>15</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>4</v>
       </c>
       <c r="D410" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E410">
         <v>28.03</v>
@@ -8694,7 +8694,7 @@
         <v>28.06</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>15</v>
       </c>
@@ -8705,7 +8705,7 @@
         <v>5</v>
       </c>
       <c r="D411" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E411">
         <v>27.3</v>
@@ -8714,7 +8714,7 @@
         <v>27.9</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>15</v>
       </c>
@@ -8725,7 +8725,7 @@
         <v>6</v>
       </c>
       <c r="D412" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E412">
         <v>27.78</v>
@@ -8734,7 +8734,7 @@
         <v>27.77</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>15</v>
       </c>
@@ -8745,7 +8745,7 @@
         <v>7</v>
       </c>
       <c r="D413" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E413">
         <v>28.54</v>
@@ -8754,7 +8754,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>15</v>
       </c>
@@ -8765,7 +8765,7 @@
         <v>8</v>
       </c>
       <c r="D414" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E414">
         <v>26.27</v>
@@ -8774,7 +8774,7 @@
         <v>26.19</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>15</v>
       </c>
@@ -8785,7 +8785,7 @@
         <v>1</v>
       </c>
       <c r="D415" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E415">
         <v>26.73</v>
@@ -8794,7 +8794,7 @@
         <v>26.82</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>15</v>
       </c>
@@ -8805,7 +8805,7 @@
         <v>2</v>
       </c>
       <c r="D416" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E416">
         <v>26.04</v>
@@ -8814,7 +8814,7 @@
         <v>25.93</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>15</v>
       </c>
@@ -8825,7 +8825,7 @@
         <v>3</v>
       </c>
       <c r="D417" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E417">
         <v>28.41</v>
@@ -8834,7 +8834,7 @@
         <v>27.8</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>15</v>
       </c>
@@ -8845,7 +8845,7 @@
         <v>4</v>
       </c>
       <c r="D418" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E418">
         <v>25</v>
@@ -8854,7 +8854,7 @@
         <v>24.93</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>15</v>
       </c>
@@ -8865,7 +8865,7 @@
         <v>5</v>
       </c>
       <c r="D419" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E419">
         <v>27.06</v>
@@ -8874,7 +8874,7 @@
         <v>27.45</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>15</v>
       </c>
@@ -8885,7 +8885,7 @@
         <v>6</v>
       </c>
       <c r="D420" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E420">
         <v>26.7</v>
@@ -8894,7 +8894,7 @@
         <v>26.47</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>15</v>
       </c>
@@ -8905,7 +8905,7 @@
         <v>7</v>
       </c>
       <c r="D421" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E421">
         <v>26.54</v>
@@ -8914,7 +8914,7 @@
         <v>26.57</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>15</v>
       </c>
@@ -8925,7 +8925,7 @@
         <v>8</v>
       </c>
       <c r="D422" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E422">
         <v>26.44</v>
@@ -8934,7 +8934,7 @@
         <v>26.58</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>15</v>
       </c>
@@ -8945,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="D423" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E423">
         <v>25.48</v>
@@ -8954,7 +8954,7 @@
         <v>25.51</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>15</v>
       </c>
@@ -8965,7 +8965,7 @@
         <v>2</v>
       </c>
       <c r="D424" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E424">
         <v>24.51</v>
@@ -8974,7 +8974,7 @@
         <v>24.74</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>15</v>
       </c>
@@ -8985,7 +8985,7 @@
         <v>3</v>
       </c>
       <c r="D425" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E425">
         <v>25.74</v>
@@ -8994,7 +8994,7 @@
         <v>26.03</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>15</v>
       </c>
@@ -9005,7 +9005,7 @@
         <v>4</v>
       </c>
       <c r="D426" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E426">
         <v>25.8</v>
@@ -9014,7 +9014,7 @@
         <v>25.67</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>15</v>
       </c>
@@ -9025,7 +9025,7 @@
         <v>5</v>
       </c>
       <c r="D427" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E427">
         <v>26.13</v>
@@ -9034,7 +9034,7 @@
         <v>26.01</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>15</v>
       </c>
@@ -9045,7 +9045,7 @@
         <v>6</v>
       </c>
       <c r="D428" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E428">
         <v>27.78</v>
@@ -9054,7 +9054,7 @@
         <v>28.03</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>15</v>
       </c>
@@ -9065,7 +9065,7 @@
         <v>7</v>
       </c>
       <c r="D429" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E429">
         <v>29.2</v>
@@ -9074,7 +9074,7 @@
         <v>28.77</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>15</v>
       </c>
@@ -9085,7 +9085,7 @@
         <v>8</v>
       </c>
       <c r="D430" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E430">
         <v>25.92</v>
@@ -9094,7 +9094,7 @@
         <v>25.75</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>15</v>
       </c>
@@ -9105,7 +9105,7 @@
         <v>1</v>
       </c>
       <c r="D431" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E431">
         <v>32.090000000000003</v>
@@ -9114,7 +9114,7 @@
         <v>32.28</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>15</v>
       </c>
@@ -9125,7 +9125,7 @@
         <v>2</v>
       </c>
       <c r="D432" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E432">
         <v>30.83</v>
@@ -9134,7 +9134,7 @@
         <v>30.92</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>15</v>
       </c>
@@ -9145,7 +9145,7 @@
         <v>3</v>
       </c>
       <c r="D433" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E433">
         <v>31.23</v>
@@ -9154,7 +9154,7 @@
         <v>31.59</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>15</v>
       </c>
@@ -9165,7 +9165,7 @@
         <v>4</v>
       </c>
       <c r="D434" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E434">
         <v>30.27</v>
@@ -9174,7 +9174,7 @@
         <v>30.28</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>15</v>
       </c>
@@ -9185,7 +9185,7 @@
         <v>5</v>
       </c>
       <c r="D435" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E435">
         <v>30.46</v>
@@ -9194,7 +9194,7 @@
         <v>30.52</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>15</v>
       </c>
@@ -9205,7 +9205,7 @@
         <v>6</v>
       </c>
       <c r="D436" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E436">
         <v>30.15</v>
@@ -9214,7 +9214,7 @@
         <v>30.14</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>15</v>
       </c>
@@ -9225,7 +9225,7 @@
         <v>7</v>
       </c>
       <c r="D437" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E437">
         <v>29.92</v>
@@ -9234,7 +9234,7 @@
         <v>29.91</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>15</v>
       </c>
@@ -9245,7 +9245,7 @@
         <v>8</v>
       </c>
       <c r="D438" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E438">
         <v>30.18</v>
@@ -9254,7 +9254,7 @@
         <v>29.84</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>15</v>
       </c>
@@ -9265,7 +9265,7 @@
         <v>1</v>
       </c>
       <c r="D439" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E439">
         <v>31.09</v>
@@ -9274,7 +9274,7 @@
         <v>31.37</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>15</v>
       </c>
@@ -9285,7 +9285,7 @@
         <v>2</v>
       </c>
       <c r="D440" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E440">
         <v>31.06</v>
@@ -9294,7 +9294,7 @@
         <v>31.15</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>15</v>
       </c>
@@ -9305,7 +9305,7 @@
         <v>3</v>
       </c>
       <c r="D441" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E441">
         <v>31.32</v>
@@ -9314,7 +9314,7 @@
         <v>31.37</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>15</v>
       </c>
@@ -9325,7 +9325,7 @@
         <v>4</v>
       </c>
       <c r="D442" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E442">
         <v>31.79</v>
@@ -9334,7 +9334,7 @@
         <v>31.36</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>15</v>
       </c>
@@ -9345,7 +9345,7 @@
         <v>5</v>
       </c>
       <c r="D443" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E443">
         <v>31.15</v>
@@ -9354,7 +9354,7 @@
         <v>31.41</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>15</v>
       </c>
@@ -9365,7 +9365,7 @@
         <v>6</v>
       </c>
       <c r="D444" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E444">
         <v>31.08</v>
@@ -9374,7 +9374,7 @@
         <v>30.86</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>15</v>
       </c>
@@ -9385,7 +9385,7 @@
         <v>7</v>
       </c>
       <c r="D445" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E445">
         <v>31.5</v>
@@ -9394,7 +9394,7 @@
         <v>31.26</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>15</v>
       </c>
@@ -9405,7 +9405,7 @@
         <v>1</v>
       </c>
       <c r="D446" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E446">
         <v>31.4</v>
@@ -9414,7 +9414,7 @@
         <v>30.87</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>15</v>
       </c>
@@ -9425,7 +9425,7 @@
         <v>2</v>
       </c>
       <c r="D447" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E447">
         <v>30.55</v>
@@ -9434,7 +9434,7 @@
         <v>30.63</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>15</v>
       </c>
@@ -9445,7 +9445,7 @@
         <v>3</v>
       </c>
       <c r="D448" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E448">
         <v>31.94</v>
@@ -9454,7 +9454,7 @@
         <v>32.020000000000003</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>15</v>
       </c>
@@ -9465,7 +9465,7 @@
         <v>4</v>
       </c>
       <c r="D449" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E449">
         <v>32.020000000000003</v>
@@ -9474,7 +9474,7 @@
         <v>32.17</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>15</v>
       </c>
@@ -9485,7 +9485,7 @@
         <v>5</v>
       </c>
       <c r="D450" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E450">
         <v>32.1</v>
@@ -9494,7 +9494,7 @@
         <v>32.4</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>15</v>
       </c>
@@ -9505,7 +9505,7 @@
         <v>6</v>
       </c>
       <c r="D451" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E451">
         <v>32.369999999999997</v>
@@ -9514,7 +9514,7 @@
         <v>32.07</v>
       </c>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>15</v>
       </c>
@@ -9525,7 +9525,7 @@
         <v>7</v>
       </c>
       <c r="D452" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E452">
         <v>32.85</v>
@@ -9534,7 +9534,7 @@
         <v>33.04</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>15</v>
       </c>
@@ -9545,7 +9545,7 @@
         <v>8</v>
       </c>
       <c r="D453" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E453">
         <v>30.39</v>
@@ -9554,7 +9554,7 @@
         <v>31.62</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>15</v>
       </c>
@@ -9565,7 +9565,7 @@
         <v>1</v>
       </c>
       <c r="D454" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E454">
         <v>32.33</v>
@@ -9574,7 +9574,7 @@
         <v>32.28</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>15</v>
       </c>
@@ -9585,7 +9585,7 @@
         <v>2</v>
       </c>
       <c r="D455" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E455">
         <v>31.49</v>
@@ -9594,7 +9594,7 @@
         <v>30.56</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>15</v>
       </c>
@@ -9605,7 +9605,7 @@
         <v>3</v>
       </c>
       <c r="D456" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E456">
         <v>32.5</v>
@@ -9614,7 +9614,7 @@
         <v>32.1</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>15</v>
       </c>
@@ -9625,7 +9625,7 @@
         <v>4</v>
       </c>
       <c r="D457" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E457">
         <v>28.24</v>
@@ -9634,7 +9634,7 @@
         <v>29.01</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>15</v>
       </c>
@@ -9645,7 +9645,7 @@
         <v>5</v>
       </c>
       <c r="D458" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E458">
         <v>33.119999999999997</v>
@@ -9654,7 +9654,7 @@
         <v>32.94</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>15</v>
       </c>
@@ -9665,7 +9665,7 @@
         <v>6</v>
       </c>
       <c r="D459" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E459">
         <v>30.59</v>
@@ -9674,7 +9674,7 @@
         <v>30.85</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>15</v>
       </c>
@@ -9685,7 +9685,7 @@
         <v>7</v>
       </c>
       <c r="D460" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E460">
         <v>31.47</v>
@@ -9694,7 +9694,7 @@
         <v>31.1</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>15</v>
       </c>
@@ -9705,7 +9705,7 @@
         <v>8</v>
       </c>
       <c r="D461" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E461">
         <v>30.28</v>
@@ -9714,7 +9714,7 @@
         <v>31.13</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>15</v>
       </c>
@@ -9725,7 +9725,7 @@
         <v>1</v>
       </c>
       <c r="D462" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E462">
         <v>32.11</v>
@@ -9734,7 +9734,7 @@
         <v>31.27</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>15</v>
       </c>
@@ -9745,7 +9745,7 @@
         <v>2</v>
       </c>
       <c r="D463" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E463">
         <v>30.01</v>
@@ -9754,7 +9754,7 @@
         <v>29.69</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>15</v>
       </c>
@@ -9765,7 +9765,7 @@
         <v>3</v>
       </c>
       <c r="D464" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E464">
         <v>30.26</v>
@@ -9774,7 +9774,7 @@
         <v>29.89</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>15</v>
       </c>
@@ -9785,7 +9785,7 @@
         <v>4</v>
       </c>
       <c r="D465" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E465">
         <v>29.83</v>
@@ -9794,7 +9794,7 @@
         <v>29.55</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>15</v>
       </c>
@@ -9805,7 +9805,7 @@
         <v>5</v>
       </c>
       <c r="D466" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E466">
         <v>30.06</v>
@@ -9814,7 +9814,7 @@
         <v>30.48</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>15</v>
       </c>
@@ -9825,7 +9825,7 @@
         <v>6</v>
       </c>
       <c r="D467" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E467">
         <v>31.04</v>
@@ -9834,7 +9834,7 @@
         <v>30.73</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>15</v>
       </c>
@@ -9845,7 +9845,7 @@
         <v>7</v>
       </c>
       <c r="D468" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E468">
         <v>32.07</v>
@@ -9854,7 +9854,7 @@
         <v>32.020000000000003</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>15</v>
       </c>
@@ -9865,7 +9865,7 @@
         <v>8</v>
       </c>
       <c r="D469" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E469">
         <v>30.31</v>
@@ -9874,7 +9874,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>15</v>
       </c>
@@ -9885,7 +9885,7 @@
         <v>1</v>
       </c>
       <c r="D470" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E470">
         <v>31</v>
@@ -9894,7 +9894,7 @@
         <v>31.36</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>15</v>
       </c>
@@ -9905,7 +9905,7 @@
         <v>2</v>
       </c>
       <c r="D471" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E471">
         <v>30.22</v>
@@ -9914,7 +9914,7 @@
         <v>30.44</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>15</v>
       </c>
@@ -9925,7 +9925,7 @@
         <v>3</v>
       </c>
       <c r="D472" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E472">
         <v>29.6</v>
@@ -9934,7 +9934,7 @@
         <v>30.25</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>15</v>
       </c>
@@ -9945,7 +9945,7 @@
         <v>4</v>
       </c>
       <c r="D473" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E473">
         <v>29.99</v>
@@ -9954,7 +9954,7 @@
         <v>29.04</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>15</v>
       </c>
@@ -9965,7 +9965,7 @@
         <v>5</v>
       </c>
       <c r="D474" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E474">
         <v>29.4</v>
@@ -9974,7 +9974,7 @@
         <v>30.07</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>15</v>
       </c>
@@ -9985,7 +9985,7 @@
         <v>6</v>
       </c>
       <c r="D475" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E475">
         <v>28.92</v>
@@ -9994,7 +9994,7 @@
         <v>28.63</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>15</v>
       </c>
@@ -10005,7 +10005,7 @@
         <v>7</v>
       </c>
       <c r="D476" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E476">
         <v>29.02</v>
@@ -10014,7 +10014,7 @@
         <v>29.17</v>
       </c>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>15</v>
       </c>
@@ -10025,7 +10025,7 @@
         <v>8</v>
       </c>
       <c r="D477" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E477">
         <v>26.89</v>
@@ -10034,7 +10034,7 @@
         <v>26.08</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>15</v>
       </c>
@@ -10045,7 +10045,7 @@
         <v>1</v>
       </c>
       <c r="D478" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E478">
         <v>29.17</v>
@@ -10054,7 +10054,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>15</v>
       </c>
@@ -10065,7 +10065,7 @@
         <v>2</v>
       </c>
       <c r="D479" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E479">
         <v>30.1</v>
@@ -10074,7 +10074,7 @@
         <v>29.84</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>15</v>
       </c>
@@ -10085,7 +10085,7 @@
         <v>3</v>
       </c>
       <c r="D480" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E480">
         <v>30.41</v>
@@ -10094,7 +10094,7 @@
         <v>30.68</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>15</v>
       </c>
@@ -10105,7 +10105,7 @@
         <v>4</v>
       </c>
       <c r="D481" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E481">
         <v>30.14</v>
@@ -10114,7 +10114,7 @@
         <v>29.31</v>
       </c>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>15</v>
       </c>
@@ -10125,7 +10125,7 @@
         <v>5</v>
       </c>
       <c r="D482" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E482">
         <v>30.13</v>
@@ -10134,7 +10134,7 @@
         <v>29.65</v>
       </c>
     </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>15</v>
       </c>
@@ -10145,7 +10145,7 @@
         <v>6</v>
       </c>
       <c r="D483" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E483">
         <v>30.15</v>
@@ -10154,7 +10154,7 @@
         <v>30.06</v>
       </c>
     </row>
-    <row r="484" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>15</v>
       </c>
@@ -10165,7 +10165,7 @@
         <v>7</v>
       </c>
       <c r="D484" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E484">
         <v>29.56</v>
@@ -10174,7 +10174,7 @@
         <v>29.55</v>
       </c>
     </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>15</v>
       </c>
@@ -10185,7 +10185,7 @@
         <v>1</v>
       </c>
       <c r="D485" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E485">
         <v>29.83</v>
@@ -10194,7 +10194,7 @@
         <v>30.1</v>
       </c>
     </row>
-    <row r="486" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>15</v>
       </c>
@@ -10205,7 +10205,7 @@
         <v>2</v>
       </c>
       <c r="D486" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E486">
         <v>29.84</v>
@@ -10214,7 +10214,7 @@
         <v>29.34</v>
       </c>
     </row>
-    <row r="487" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>15</v>
       </c>
@@ -10225,7 +10225,7 @@
         <v>3</v>
       </c>
       <c r="D487" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E487">
         <v>30.07</v>
@@ -10234,7 +10234,7 @@
         <v>30.27</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>15</v>
       </c>
@@ -10245,7 +10245,7 @@
         <v>4</v>
       </c>
       <c r="D488" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E488">
         <v>31.68</v>
@@ -10254,7 +10254,7 @@
         <v>30.5</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>15</v>
       </c>
@@ -10265,7 +10265,7 @@
         <v>5</v>
       </c>
       <c r="D489" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E489">
         <v>32.159999999999997</v>
@@ -10274,7 +10274,7 @@
         <v>31.9</v>
       </c>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>15</v>
       </c>
@@ -10285,7 +10285,7 @@
         <v>6</v>
       </c>
       <c r="D490" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E490">
         <v>30.18</v>
@@ -10294,7 +10294,7 @@
         <v>30.21</v>
       </c>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>15</v>
       </c>
@@ -10305,7 +10305,7 @@
         <v>7</v>
       </c>
       <c r="D491" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E491">
         <v>29.25</v>
@@ -10314,7 +10314,7 @@
         <v>30.62</v>
       </c>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>15</v>
       </c>
@@ -10325,7 +10325,7 @@
         <v>8</v>
       </c>
       <c r="D492" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E492">
         <v>29.43</v>
@@ -10334,7 +10334,7 @@
         <v>30.13</v>
       </c>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>15</v>
       </c>
@@ -10345,7 +10345,7 @@
         <v>1</v>
       </c>
       <c r="D493" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E493">
         <v>26.16</v>
@@ -10354,7 +10354,7 @@
         <v>26.23</v>
       </c>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>15</v>
       </c>
@@ -10365,7 +10365,7 @@
         <v>2</v>
       </c>
       <c r="D494" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E494">
         <v>23.5</v>
@@ -10374,7 +10374,7 @@
         <v>23.31</v>
       </c>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>15</v>
       </c>
@@ -10385,7 +10385,7 @@
         <v>3</v>
       </c>
       <c r="D495" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E495">
         <v>31.05</v>
@@ -10394,7 +10394,7 @@
         <v>31.39</v>
       </c>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>15</v>
       </c>
@@ -10405,7 +10405,7 @@
         <v>4</v>
       </c>
       <c r="D496" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E496">
         <v>22.49</v>
@@ -10414,7 +10414,7 @@
         <v>22.7</v>
       </c>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>15</v>
       </c>
@@ -10425,7 +10425,7 @@
         <v>5</v>
       </c>
       <c r="D497" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E497">
         <v>29.3</v>
@@ -10434,7 +10434,7 @@
         <v>30.07</v>
       </c>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>15</v>
       </c>
@@ -10445,7 +10445,7 @@
         <v>6</v>
       </c>
       <c r="D498" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E498">
         <v>22.71</v>
@@ -10454,7 +10454,7 @@
         <v>22.75</v>
       </c>
     </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>15</v>
       </c>
@@ -10465,7 +10465,7 @@
         <v>7</v>
       </c>
       <c r="D499" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E499">
         <v>28</v>
@@ -10474,7 +10474,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>15</v>
       </c>
@@ -10485,7 +10485,7 @@
         <v>8</v>
       </c>
       <c r="D500" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E500">
         <v>29.74</v>
@@ -10494,7 +10494,7 @@
         <v>29.65</v>
       </c>
     </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>15</v>
       </c>
@@ -10505,7 +10505,7 @@
         <v>1</v>
       </c>
       <c r="D501" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E501">
         <v>19.579999999999998</v>
@@ -10514,7 +10514,7 @@
         <v>19.41</v>
       </c>
     </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>15</v>
       </c>
@@ -10525,7 +10525,7 @@
         <v>2</v>
       </c>
       <c r="D502" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E502">
         <v>23.66</v>
@@ -10534,7 +10534,7 @@
         <v>22.97</v>
       </c>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>15</v>
       </c>
@@ -10545,7 +10545,7 @@
         <v>3</v>
       </c>
       <c r="D503" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E503">
         <v>26.99</v>
@@ -10554,7 +10554,7 @@
         <v>26.4</v>
       </c>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>15</v>
       </c>
@@ -10565,7 +10565,7 @@
         <v>4</v>
       </c>
       <c r="D504" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E504">
         <v>22.04</v>
@@ -10574,7 +10574,7 @@
         <v>22.63</v>
       </c>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>15</v>
       </c>
@@ -10585,7 +10585,7 @@
         <v>5</v>
       </c>
       <c r="D505" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E505">
         <v>21.61</v>
@@ -10594,7 +10594,7 @@
         <v>22.12</v>
       </c>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>15</v>
       </c>
@@ -10605,7 +10605,7 @@
         <v>6</v>
       </c>
       <c r="D506" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E506">
         <v>21.47</v>
@@ -10614,7 +10614,7 @@
         <v>21.17</v>
       </c>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>15</v>
       </c>
@@ -10625,7 +10625,7 @@
         <v>7</v>
       </c>
       <c r="D507" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E507">
         <v>28.55</v>
@@ -10634,7 +10634,7 @@
         <v>28.27</v>
       </c>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>15</v>
       </c>
@@ -10645,7 +10645,7 @@
         <v>8</v>
       </c>
       <c r="D508" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E508">
         <v>21.24</v>
